--- a/docs/harness/wirelist/CSB3-wirelist.xlsx
+++ b/docs/harness/wirelist/CSB3-wirelist.xlsx
@@ -1206,7 +1206,7 @@
       <c r="AD3" s="38" t="inlineStr"/>
       <c r="AE3" s="38" t="inlineStr">
         <is>
-          <t>splice sp_csb_gnd named in SoT</t>
+          <t>splice sp_csb_gnd: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF3" s="38" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="H7" s="25" t="inlineStr">
         <is>
-          <t>o1</t>
+          <t>OUT1</t>
         </is>
       </c>
       <c r="I7" s="26" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="H8" s="41" t="inlineStr">
         <is>
-          <t>o2</t>
+          <t>OUT2</t>
         </is>
       </c>
       <c r="I8" s="42" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AE10" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_CRUISE_STALK_C1: EWD Cruise control switch (C14, comb. switch) pin 5 W (white); splice sp_cruise_ladder named in SoT</t>
+          <t>flying lead FL_CRUISE_STALK_C1: EWD Cruise control switch (C14, comb. switch) pin 5 W (white); splice sp_cruise_ladder: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF10" s="54" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="AE12" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_CRUISE_STALK_C17: EWD Cruise control switch (C14, comb. switch) pin 17 BR (brown); splice sp_csb_gnd named in SoT</t>
+          <t>flying lead FL_CRUISE_STALK_C17: EWD Cruise control switch (C14, comb. switch) pin 17 BR (brown); splice sp_csb_gnd: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF12" s="54" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="N13" s="28" t="inlineStr">
         <is>
-          <t>i1</t>
+          <t>IN1</t>
         </is>
       </c>
       <c r="O13" s="29" t="inlineStr">
@@ -2350,12 +2350,12 @@
       <c r="P13" s="29" t="inlineStr"/>
       <c r="Q13" s="30" t="inlineStr">
         <is>
-          <t>opto8.i1</t>
+          <t>opto8.IN1</t>
         </is>
       </c>
       <c r="R13" s="31" t="inlineStr">
         <is>
-          <t>Brake on +12 V (opto8 i1)</t>
+          <t>Brake on +12 V (opto8 IN1)</t>
         </is>
       </c>
       <c r="S13" s="32" t="inlineStr"/>
@@ -2515,7 +2515,7 @@
       <c r="AD14" s="54" t="inlineStr"/>
       <c r="AE14" s="54" t="inlineStr">
         <is>
-          <t>splice sp_cruise_ladder named in SoT</t>
+          <t>splice sp_cruise_ladder: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF14" s="54" t="inlineStr">
@@ -2626,7 +2626,7 @@
       <c r="AD15" s="38" t="inlineStr"/>
       <c r="AE15" s="38" t="inlineStr">
         <is>
-          <t>splice sp_cruise_ladder named in SoT</t>
+          <t>splice sp_cruise_ladder: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF15" s="38" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="N16" s="44" t="inlineStr">
         <is>
-          <t>com1</t>
+          <t>COM1</t>
         </is>
       </c>
       <c r="O16" s="45" t="inlineStr">
@@ -2739,7 +2739,7 @@
       <c r="AD16" s="54" t="inlineStr"/>
       <c r="AE16" s="54" t="inlineStr">
         <is>
-          <t>splice sp_csb_gnd named in SoT</t>
+          <t>splice sp_csb_gnd: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF16" s="54" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="H38" s="41" t="inlineStr">
         <is>
-          <t>com2</t>
+          <t>COM2</t>
         </is>
       </c>
       <c r="I38" s="42" t="inlineStr">
@@ -4241,12 +4241,12 @@
       <c r="P38" s="45" t="inlineStr"/>
       <c r="Q38" s="46" t="inlineStr">
         <is>
-          <t>opto8.com2</t>
+          <t>opto8.COM2</t>
         </is>
       </c>
       <c r="R38" s="47" t="inlineStr">
         <is>
-          <t>spare (opto8 com2)</t>
+          <t>spare (opto8 COM2)</t>
         </is>
       </c>
       <c r="S38" s="48" t="inlineStr"/>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="H39" s="25" t="inlineStr">
         <is>
-          <t>i3</t>
+          <t>IN3</t>
         </is>
       </c>
       <c r="I39" s="26" t="inlineStr">
@@ -4312,12 +4312,12 @@
       <c r="P39" s="29" t="inlineStr"/>
       <c r="Q39" s="30" t="inlineStr">
         <is>
-          <t>opto8.i3</t>
+          <t>opto8.IN3</t>
         </is>
       </c>
       <c r="R39" s="31" t="inlineStr">
         <is>
-          <t>spare (opto8 i3)</t>
+          <t>spare (opto8 IN3)</t>
         </is>
       </c>
       <c r="S39" s="32" t="inlineStr"/>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="H40" s="41" t="inlineStr">
         <is>
-          <t>i4</t>
+          <t>IN4</t>
         </is>
       </c>
       <c r="I40" s="42" t="inlineStr">
@@ -4383,12 +4383,12 @@
       <c r="P40" s="45" t="inlineStr"/>
       <c r="Q40" s="46" t="inlineStr">
         <is>
-          <t>opto8.i4</t>
+          <t>opto8.IN4</t>
         </is>
       </c>
       <c r="R40" s="47" t="inlineStr">
         <is>
-          <t>spare (opto8 i4)</t>
+          <t>spare (opto8 IN4)</t>
         </is>
       </c>
       <c r="S40" s="48" t="inlineStr"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="H41" s="25" t="inlineStr">
         <is>
-          <t>i5</t>
+          <t>IN5</t>
         </is>
       </c>
       <c r="I41" s="26" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="P41" s="29" t="inlineStr"/>
       <c r="Q41" s="30" t="inlineStr">
         <is>
-          <t>opto8.i5</t>
+          <t>opto8.IN5</t>
         </is>
       </c>
       <c r="R41" s="31" t="inlineStr">
         <is>
-          <t>spare (opto8 i5)</t>
+          <t>spare (opto8 IN5)</t>
         </is>
       </c>
       <c r="S41" s="32" t="inlineStr"/>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="H42" s="41" t="inlineStr">
         <is>
-          <t>i6</t>
+          <t>IN6</t>
         </is>
       </c>
       <c r="I42" s="42" t="inlineStr">
@@ -4525,12 +4525,12 @@
       <c r="P42" s="45" t="inlineStr"/>
       <c r="Q42" s="46" t="inlineStr">
         <is>
-          <t>opto8.i6</t>
+          <t>opto8.IN6</t>
         </is>
       </c>
       <c r="R42" s="47" t="inlineStr">
         <is>
-          <t>spare (opto8 i6)</t>
+          <t>spare (opto8 IN6)</t>
         </is>
       </c>
       <c r="S42" s="48" t="inlineStr"/>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H43" s="25" t="inlineStr">
         <is>
-          <t>i7</t>
+          <t>IN7</t>
         </is>
       </c>
       <c r="I43" s="26" t="inlineStr">
@@ -4596,12 +4596,12 @@
       <c r="P43" s="29" t="inlineStr"/>
       <c r="Q43" s="30" t="inlineStr">
         <is>
-          <t>opto8.i7</t>
+          <t>opto8.IN7</t>
         </is>
       </c>
       <c r="R43" s="31" t="inlineStr">
         <is>
-          <t>spare (opto8 i7)</t>
+          <t>spare (opto8 IN7)</t>
         </is>
       </c>
       <c r="S43" s="32" t="inlineStr"/>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H44" s="41" t="inlineStr">
         <is>
-          <t>i8</t>
+          <t>IN8</t>
         </is>
       </c>
       <c r="I44" s="42" t="inlineStr">
@@ -4667,12 +4667,12 @@
       <c r="P44" s="45" t="inlineStr"/>
       <c r="Q44" s="46" t="inlineStr">
         <is>
-          <t>opto8.i8</t>
+          <t>opto8.IN8</t>
         </is>
       </c>
       <c r="R44" s="47" t="inlineStr">
         <is>
-          <t>spare (opto8 i8)</t>
+          <t>spare (opto8 IN8)</t>
         </is>
       </c>
       <c r="S44" s="48" t="inlineStr"/>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="H45" s="25" t="inlineStr">
         <is>
-          <t>o3</t>
+          <t>OUT3</t>
         </is>
       </c>
       <c r="I45" s="26" t="inlineStr">
@@ -4738,12 +4738,12 @@
       <c r="P45" s="29" t="inlineStr"/>
       <c r="Q45" s="30" t="inlineStr">
         <is>
-          <t>opto8.o3</t>
+          <t>opto8.OUT3</t>
         </is>
       </c>
       <c r="R45" s="31" t="inlineStr">
         <is>
-          <t>spare (opto8 o3)</t>
+          <t>spare (opto8 OUT3)</t>
         </is>
       </c>
       <c r="S45" s="32" t="inlineStr"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="H46" s="41" t="inlineStr">
         <is>
-          <t>o4</t>
+          <t>OUT4</t>
         </is>
       </c>
       <c r="I46" s="42" t="inlineStr">
@@ -4809,12 +4809,12 @@
       <c r="P46" s="45" t="inlineStr"/>
       <c r="Q46" s="46" t="inlineStr">
         <is>
-          <t>opto8.o4</t>
+          <t>opto8.OUT4</t>
         </is>
       </c>
       <c r="R46" s="47" t="inlineStr">
         <is>
-          <t>spare (opto8 o4)</t>
+          <t>spare (opto8 OUT4)</t>
         </is>
       </c>
       <c r="S46" s="48" t="inlineStr"/>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="H47" s="25" t="inlineStr">
         <is>
-          <t>o5</t>
+          <t>OUT5</t>
         </is>
       </c>
       <c r="I47" s="26" t="inlineStr">
@@ -4880,12 +4880,12 @@
       <c r="P47" s="29" t="inlineStr"/>
       <c r="Q47" s="30" t="inlineStr">
         <is>
-          <t>opto8.o5</t>
+          <t>opto8.OUT5</t>
         </is>
       </c>
       <c r="R47" s="31" t="inlineStr">
         <is>
-          <t>spare (opto8 o5)</t>
+          <t>spare (opto8 OUT5)</t>
         </is>
       </c>
       <c r="S47" s="32" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="H48" s="41" t="inlineStr">
         <is>
-          <t>o6</t>
+          <t>OUT6</t>
         </is>
       </c>
       <c r="I48" s="42" t="inlineStr">
@@ -4951,12 +4951,12 @@
       <c r="P48" s="45" t="inlineStr"/>
       <c r="Q48" s="46" t="inlineStr">
         <is>
-          <t>opto8.o6</t>
+          <t>opto8.OUT6</t>
         </is>
       </c>
       <c r="R48" s="47" t="inlineStr">
         <is>
-          <t>spare (opto8 o6)</t>
+          <t>spare (opto8 OUT6)</t>
         </is>
       </c>
       <c r="S48" s="48" t="inlineStr"/>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="H49" s="25" t="inlineStr">
         <is>
-          <t>o7</t>
+          <t>OUT7</t>
         </is>
       </c>
       <c r="I49" s="26" t="inlineStr">
@@ -5022,12 +5022,12 @@
       <c r="P49" s="29" t="inlineStr"/>
       <c r="Q49" s="30" t="inlineStr">
         <is>
-          <t>opto8.o7</t>
+          <t>opto8.OUT7</t>
         </is>
       </c>
       <c r="R49" s="31" t="inlineStr">
         <is>
-          <t>spare (opto8 o7)</t>
+          <t>spare (opto8 OUT7)</t>
         </is>
       </c>
       <c r="S49" s="32" t="inlineStr"/>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H50" s="41" t="inlineStr">
         <is>
-          <t>o8</t>
+          <t>OUT8</t>
         </is>
       </c>
       <c r="I50" s="42" t="inlineStr">
@@ -5093,12 +5093,12 @@
       <c r="P50" s="45" t="inlineStr"/>
       <c r="Q50" s="46" t="inlineStr">
         <is>
-          <t>opto8.o8</t>
+          <t>opto8.OUT8</t>
         </is>
       </c>
       <c r="R50" s="47" t="inlineStr">
         <is>
-          <t>spare (opto8 o8)</t>
+          <t>spare (opto8 OUT8)</t>
         </is>
       </c>
       <c r="S50" s="48" t="inlineStr"/>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="L3" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="L4" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/CSB3-wirelist.xlsx
+++ b/docs/harness/wirelist/CSB3-wirelist.xlsx
@@ -1403,7 +1403,7 @@
       </c>
       <c r="R5" s="31" t="inlineStr">
         <is>
-          <t>+12V CSB 5A (LOGIC BUS2-5)</t>
+          <t>+12V CSB3 +12 V (LOGIC BUS2-5)</t>
         </is>
       </c>
       <c r="S5" s="32" t="inlineStr"/>

--- a/docs/harness/wirelist/CSB3-wirelist.xlsx
+++ b/docs/harness/wirelist/CSB3-wirelist.xlsx
@@ -1639,7 +1639,7 @@
       </c>
       <c r="V7" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W7" s="34" t="inlineStr"/>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="V8" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W8" s="50" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="V9" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W9" s="34" t="inlineStr"/>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="V10" s="50" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W10" s="50" t="inlineStr"/>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="V11" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W11" s="34" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="V12" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="W12" s="50" t="inlineStr"/>
@@ -2365,14 +2365,10 @@
       </c>
       <c r="V13" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W13" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W13" s="34" t="inlineStr"/>
       <c r="X13" s="34" t="inlineStr">
         <is>
           <t>Blue-White</t>
@@ -2498,7 +2494,7 @@
       </c>
       <c r="V14" s="50" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W14" s="50" t="inlineStr"/>
@@ -2609,7 +2605,7 @@
       </c>
       <c r="V15" s="34" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W15" s="34" t="inlineStr"/>

--- a/docs/harness/wirelist/CSB3-wirelist.xlsx
+++ b/docs/harness/wirelist/CSB3-wirelist.xlsx
@@ -752,7 +752,7 @@
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="36" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
     <col width="32" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="8" customWidth="1" min="20" max="20"/>
@@ -1170,12 +1170,12 @@
       <c r="P3" s="29" t="inlineStr"/>
       <c r="Q3" s="30" t="inlineStr">
         <is>
-          <t>STUD.M6-ECU</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="R3" s="31" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>Chassis GND (POWER box NEG bar M8 stud (glove box))</t>
         </is>
       </c>
       <c r="S3" s="32" t="inlineStr">
@@ -2219,12 +2219,12 @@
       <c r="P12" s="45" t="inlineStr"/>
       <c r="Q12" s="46" t="inlineStr">
         <is>
-          <t>STUD.M6-ECU</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="R12" s="47" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>Chassis GND (POWER box NEG bar M8 stud (glove box))</t>
         </is>
       </c>
       <c r="S12" s="48" t="inlineStr">
@@ -2699,12 +2699,12 @@
       <c r="P16" s="45" t="inlineStr"/>
       <c r="Q16" s="46" t="inlineStr">
         <is>
-          <t>STUD.M6-ECU</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="R16" s="47" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>Chassis GND (POWER box NEG bar M8 stud (glove box))</t>
         </is>
       </c>
       <c r="S16" s="48" t="inlineStr">
@@ -5136,7 +5136,7 @@
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
@@ -5345,12 +5345,12 @@
       </c>
       <c r="D4" s="46" t="inlineStr">
         <is>
-          <t>STUD.M6-ECU</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="E4" s="47" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>Chassis GND (POWER box NEG bar M8 stud (glove box))</t>
         </is>
       </c>
       <c r="F4" s="48" t="n">
